--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1437-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1437-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F4299A5-5244-4F9B-9961-CCF1EAF391A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9DC05E4-10E1-4B56-8607-AD714975DB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{7D5C0819-1EB8-40EA-A46F-3E61324EFBBF}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{6BAEA3B1-4A74-4136-BE51-C4E816A4E380}"/>
   </bookViews>
   <sheets>
     <sheet name="1437-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1552,30 +1552,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AFAE3AF-731F-4971-A334-078BCD22245D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03F2A61-BD80-4C94-8D69-6047CA6D32D6}">
   <dimension ref="A1:X49"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1609,7 +1609,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1645,7 +1645,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1765,7 +1765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1873,7 +1873,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>30</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="49">
         <v>2024</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="51">
         <v>2023</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2022</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="51">
         <v>2021</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="49">
         <v>2020</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="51">
         <v>2019</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
         <v>2018</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2017</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="41"/>
       <c r="B17" s="42"/>
       <c r="C17" s="21" t="s">
@@ -2625,7 +2625,7 @@
       <c r="W17" s="48"/>
       <c r="X17" s="46"/>
     </row>
-    <row r="18" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="49">
         <v>2016</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="51">
         <v>2015</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="49">
         <v>2014</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="51">
         <v>2013</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="49">
         <v>2012</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="51">
         <v>2011</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="49">
         <v>2010</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="51">
         <v>2009</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="49">
         <v>2008</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="51">
         <v>2007</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="49">
         <v>2006</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="51">
         <v>2005</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="49">
         <v>2004</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="51">
         <v>2003</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="49">
         <v>2002</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="51">
         <v>2001</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="49">
         <v>2000</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="51">
         <v>1999</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="49">
         <v>1998</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="51">
         <v>1997</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="49">
         <v>1996</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="51">
         <v>1995</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="49">
         <v>1994</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="51">
         <v>1993</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="49">
         <v>1992</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="51">
         <v>1991</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="49">
         <v>1990</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="51">
         <v>1989</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="49">
         <v>1988</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="51">
         <v>1987</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="49">
         <v>1985</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="51" t="s">
         <v>55</v>
       </c>
